--- a/quality_reports/cribado.xlsx
+++ b/quality_reports/cribado.xlsx
@@ -15,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$1:$C$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Candidatos'!$A$1:$H$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Candidatos'!$A$1:$H$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Etapa2_titulo'!$A$1:$H$1321</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Etapa3_resumen'!$A$1:$H$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Etapa3_resumen'!$A$1:$H$196</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Etapa1_reglas'!$A$1:$B$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="C7" t="inlineStr"/>
     </row>
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1488,8 +1488,1924 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>35444073</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy for empyema caused by carbapenem-resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Bioscience trends</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>10.5582/bst.2022.01147</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>case: post-pneumonectomy empyema with broncho-pleural fistula, carbapenem-resistant</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35444073/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>36175406</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantation in a toddler.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Nature communications</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>10.1093/nar/gkx343</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>case: XDR P. aeruginosa infection treated to allow liver transplantation</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36175406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>35529052</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Combination of phage therapy and cefiderocol to successfully treat Pseudomonas aeruginosa cranial osteomyelitis.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>JAC-antimicrobial resistance</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>10.1093/jacamr/dlac046</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>case: 25-year-old, cranial osteomyelitis after electrocution, phage plus cefiderocol</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35529052/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>35869081</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudomonas aeruginosa infection.</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Nature communications</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>10.3389/fphar.2020.578823</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>case: pandrug-resistant spinal bone and joint infection, personalised phage</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35869081/</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>36578069</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis colonized with Pseudomonas aeruginosa: study protocol for a phase 1b/2, multicenter, randomized, double-blind, placebo-controlled trial.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Trials</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>10.1016/S1473-3099(20)30330-3</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>randomised placebo-controlled trial protocol, single intravenous dose, ~72 adults with cystic fibrosis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36578069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>35547216</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Treatment of Multidrug-Resistant Pseudomonas aeruginosa Femur Osteomyelitis-A Case Report.</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Frontiers in medicine</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>10.3389/fmed.2020.00342</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>case: post-traumatic femoral osteomyelitis, BFC 1.10 with ceftazidime-avibactam</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/35547216/</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>36861092</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Application of Phage Therapy in a Case of a Chronic Hip-Prosthetic Joint Infection due to Pseudomonas aeruginosa: An Italian Real-Life Experience and In Vitro Analysis.</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Open forum infectious diseases</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>10.1093/ofid/ofad051</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>case: 62-year-old, chronic hip prosthetic joint infection, phage with meropenem</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36861092/</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>37515541</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy for Pan-Drug-Resistant Pseudomonas aeruginosa in Two Persons With Cystic Fibrosis.</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Journal of investigative medicine high impact case reports</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>10.1101/2023.01.23.22283996</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>two persons with cystic fibrosis, pandrug-resistant P. aeruginosa</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37515541/</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>37275366</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Case report: Analysis of phage therapy failure in a patient with a Pseudomonas aeruginosa prosthetic vascular graft infection.</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Frontiers in medicine</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>10.1007/978-1-60327-164-6_7</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>case: phage therapy failure in prosthetic vascular graft infection, PT07/14-01/PNM</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37275366/</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>36082999</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Development of Host Immune Response to Bacteriophage in a Lung Transplant Recipient on Adjunctive Phage Therapy for a Multidrug-Resistant Pneumonia.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>The Journal of infectious diseases</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10.1093/infdis/jiac368</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>lung transplant recipient on adjunctive phage; phage-specific CD4 T cells and immunoglobulin</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36082999/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>36636832</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Microbial biotechnology</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>10.1111/1751-7915.14217</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>first-in-human dsRNA phage phiYY in a 40-year-old with interstitial lung disease</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/36636832/</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>37369702</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Personalized aerosolised bacteriophage treatment of a chronic lung infection due to multidrug-resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Nature communications</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>10.1093/jac/dkr198</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>case: 41-year-old with Kartagener syndrome, aerosolised personalised phage</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37369702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>37409241</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Transplantation for Common Variable Immunodeficiency Despite Maximal Treatment Including IgM/IgA-Enriched Immunoglobulins and Bacteriophage Therapy.</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Infection and drug resistance</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>10.1111/bph.15526</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>case: refractory bronchopulmonary infection after lung transplant for common variable immunodeficiency</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37409241/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>37562400</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Refractory Pseudomonas aeruginosa infections treated with phage PASA16: A compassionate use case series.</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Med (New York, N.Y.)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.medj.2023.07.002</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>compassionate-use case series treated with phage PASA16</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37562400/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>37160359</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial and nebulised bacteriophage treatment in children with cystic fibrosis and Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>BMJ open respiratory research</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>10.1016/j.resmic.2018.05.001</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>single-arm open-label trial, intrabronchial and nebulised phage in children with cystic fibrosis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37160359/</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>37243293</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Driveline Infection.</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Viruses</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-021-22814-9</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>case: left ventricular assist device infection, phage-antibiotic combination</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/37243293/</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>39491599</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the PHAGEinLYON Clinic programme.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>International journal of antimicrobial agents</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10.1016/j.ijantimicag.2024.107372</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>PHAGEinLYON programme; all 2022 phage therapy requests collected prospectively</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39491599/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>38917792</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Neutralizing antibodies after nebulized phage therapy in cystic fibrosis patients.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Med (New York, N.Y.)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10.1016/j.medj.2024.05.017</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>neutralising antibodies after nebulised phage therapy in cystic fibrosis patients</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38917792/</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>38302552</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Optimized preparation pipeline for emergency phage therapy against Pseudomonas aeruginosa at Yale University.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Scientific reports</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10.1016/j.chembiol.2022.06.003</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Yale emergency phage therapy preparation pipeline; programme report with treated patients</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38302552/</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>39066242</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Phage Therapy in a Burn Patient Colonized with Extensively Drug-Resistant Pseudomonas aeruginosa Responsible for Relapsing Ventilator-Associated Pneumonia and Bacteriemia.</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Viruses</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.chom.2017.06.018</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>case: burn patient, XDR P. aeruginosa relapsing ventilator-associated pneumonia</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39066242/</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>39452183</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial Stent.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Antibiotics (Basel, Switzerland)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>10.3389/fmicb.2019.01674</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>case: recurrent Pseudomonas septicaemia with arterial stent, phage-meropenem</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39452183/</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>38470133</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five cases.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Antimicrobial agents and chemotherapy</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10.1128/mbio.02441-21</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>retrospective series: five ventricular assist device infections, ineffective phage therapy</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38470133/</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>39074617</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Virus research</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10.1128/cmr.00138-00118</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>safety, tolerability and potential efficacy of bronchoscopic and nebulised phage administration</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39074617/</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>38066373</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respiratory Tract of an Infant.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Methods in molecular biology (Clifton, N.J.)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10.1007/978-1-60327-164-6_14</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>case: 3-month-old girl, severe bronchitis after tracheostomy, consecutive phage and antibiotics</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38066373/</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>38305316</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>[Not Available].</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Ugeskrift for laeger</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>10.61409/V09230617</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>title was a placeholder; abstract confirms a case report of chronic relapsing prosthetic aortic graft infection treated with two lytic antipseudomonal phages</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/38305316/</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>41022989</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>A case report of bacteriophage therapy for the treatment of lung infection due to carbapenem-resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Scientific reports</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>10.1186/2052-0492-1-2</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>case report: phage for carbapenem-resistant P. aeruginosa lung infection</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41022989/</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>40639454</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>A feasibility study for personalized phage therapy against drug-resistant bacteria in Japan.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Journal of infection and chemotherapy : official journal of the Japan Society of Chemotherapy</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>10.1016/j.jiac.2025.102770</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>observational feasibility study of personalised phage therapy in Japan</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40639454/</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>40975185</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and proposed solutions.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>International journal of antimicrobial agents</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>10.1016/j.ijantimicag.2025.107629</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>no abstract; cannot be judged, advanced rather than excluded</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40975185/</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>40368965</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Adjunctive phage therapy improves antibiotic treatment of ventilator-associated-pneumonia with Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Nature communications</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>10.1016/j.ijantimicag.2023.106856</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>adjunctive phage in ventilator-associated pneumonia</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40368965/</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>39965256</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy for Chronic Mastoiditis.</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Otology &amp; neurotology : official publication of the American Otological Society, American Neurotology Society [and] European Academy of Otology and Neurotology</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>10.1097/MAO.0000000000004417</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>case: 47-year-old, intratympanic phage for chronic mastoiditis from MDR P. aeruginosa</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39965256/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>40301561</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Personalized inhaled bacteriophage therapy for treatment of multidrug-resistant Pseudomonas aeruginosa in cystic fibrosis.</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Nature medicine</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>10.1038/s41591-025-03678-8</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>personalised inhaled phage for MDR P. aeruginosa in cystic fibrosis</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40301561/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>39861912</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Viruses</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10.1128/aac.02071-21</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>case: recurrent P. aeruginosa Bentall endocarditis, phage as rescue</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39861912/</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>41479406</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Phage therapy of perinephric abscess in kidney transplantation recipients caused by drug-resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>mLife</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>10.1002/mlf2.70042</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>two cases: perinephric abscess in kidney transplant recipients</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41479406/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>40593506</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Phage therapy with nebulized cocktail BX004-A for chronic Pseudomonas aeruginosa infections in cystic fibrosis: a randomized first-in-human trial.</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Nature communications</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>10.1093/gigascience/giac076</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>BX004-A randomised first-in-human trial in cystic fibrosis</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40593506/</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>39740667</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Randomized double-blind study on safety and tolerability of TP-102 phage cocktail in patients with infected and non-infected diabetic foot ulcers.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Med (New York, N.Y.)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10.1016/j.medj.2024.11.018</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>randomised double-blind trial of TP-102 in patients with diabetic foot ulcers</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39740667/</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>41244966</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage intervention.</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>ASM case reports</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>10.1038/s41591-021-01403-9</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>case: acute rejection resolved in a bilateral lung transplant recipient after phage</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41244966/</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>39834667</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Successful Treatment of a Patient With Chronic Bronchiectasis Using an Induced Native Phage Cocktail: A Case Report.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Cureus</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>10.7759/cureus.77681</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>case: chronic bronchiectasis treated with an induced native phage cocktail</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/39834667/</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>40899889</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>[Clinical efficiency of polyvalent piobacteriophage in the complex treatment of nosocomial sinusitis].</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Vestnik otorinolaringologii</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>10.17116/otorino20259004133</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>polyvalent pyobacteriophage in 30 intensive-care patients with nosocomial sinusitis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40899889/</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>42070625</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Adjuvant multisite bacteriophage cocktail administration as salvage treatment in a patient with a multidrug-resistant Pseudomonas aeruginosa frontal relapsing complex osteitis.</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>International journal of infectious diseases : IJID : official publication of the International Society for Infectious Diseases</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.ijid.2026.108756</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>case: 37-year-old man, multisite phage cocktail salvage for MDR bone infection</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42070625/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>40810649</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy in clinical practice: case studies of Pseudomonas aeruginosa infections.</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Journal of chemotherapy (Florence, Italy)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>10.1080/1120009X.2025.2547147</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>clinical practice case studies of P. aeruginosa infections</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/40810649/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>42263718</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first experience with cefepime-zidebactam alongside phage therapy in the USA.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>The Lancet. Infectious diseases</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>10.1016/S1473-3099(26)00176-3</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>case: calciphylaxis with NDM-1 P. aeruginosa, cefepime-zidebactam alongside phage</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42263718/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>42364990</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosthetic joint infection using personalized bacteriophage treatment.</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Nature communications</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>10.1038/s41467-026-74326-z</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>chronic suppression of MDR P. aeruginosa prosthetic joint infection with personalised phage</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/42364990/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>41853116</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infection with adjunctive bacteriophage therapy.</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>ASM case reports</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>10.1093/jacamr/dlac046</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infection</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41853116/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>41667461</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Ecological partitioning enables phage-antibiotic cooperation in a human Pseudomonas infection.</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Nature communications</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>10.1093/bioinformatics/btt656</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>longitudinal multiomic case analysis of a man in his seventies on phage-antibiotic therapy</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41667461/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>41589298</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Pan-Resistant Pseudomonas aeruginosa Septic Shock in a Critically Ill Patient: A Case Report.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Clinical medicine insights. Case reports</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>10.1177/11795476251411094</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>case report: pan-resistant P. aeruginosa septic shock in a critically ill patient</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41589298/</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>41510198</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Pharmacodynamic individualization of phage therapy against a KPC-5-producing Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>JAC-antimicrobial resistance</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>10.3390/ph14101019</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>pharmacodynamic individualisation against a KPC-5-producing isolate; clinical assessment</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41510198/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>41565011</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infection Caused by Multidrug-Resistant Pseudomonas aeruginosa in a 2-Year-Old Child.</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>The Journal of pediatrics</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>10.1016/j.jpeds.2026.115005</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>case: recalcitrant intra-abdominal MDR infection in a paediatric patient</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41565011/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>41513696</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Nature communications</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>10.1128/jcm.22.6.996-1006.1985</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>case: refractory mediastinitis and vascular graft infection, bespoke phage-antibiotic</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>https://pubmed.ncbi.nlm.nih.gov/41513696/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H22"/>
+  <autoFilter ref="A1:H70"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -51871,7 +53787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -53601,27 +55517,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28583189</t>
+          <t>35040388</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas aeruginosa septicaemia in a patient with acute kidney injury-a case report.</t>
+          <t>Novel investigational treatments for ventilator-associated pneumonia and critically ill patients in the intensive care unit.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>no abstract; title reports phage treatment of septicaemia in a named patient</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -53631,39 +55547,35 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28992111</t>
+          <t>35041506</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Refractory Pseudomonas Bacteremia in a 2-Year-Old Sterilized by Bacteriophage Therapy.</t>
+          <t>Considerations for the Use of Phage Therapy in Clinical Practice.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>case: pediatric refractory MDR P. aeruginosa bacteraemia, 2-phage cocktail</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -53673,39 +55585,35 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>29588855</t>
+          <t>35150435</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
+          <t>Therapeutic Strategies for Emerging Multidrug-Resistant Pseudomonas aeruginosa.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>case: prosthetic vascular graft infection treated with phage</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -53715,39 +55623,35 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>30060002</t>
+          <t>35165237</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selected cocktail of bacteriophages.</t>
+          <t>Advancing bacteriophages as a treatment of antibiotic-resistant bacterial pulmonary infections.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>no abstract; title reports XDR P. aeruginosa bone and joint infection with local phage</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -53757,7 +55661,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
+          <t>2026-08-04T07:11:12</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -53765,27 +55669,27 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>30131795</t>
+          <t>35258339</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
+          <t>Complete Genome Sequence of Pseudomonas aeruginosa Bacteriophage PASA16, Used in Multiple Phage Therapy Treatments Globally.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>adapted phages for urinary tract infection; abstract does not settle whether patients were treated</t>
+          <t>laboratory study: genome announcement, formulation, cocktail design or platform technology; no patients treated</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -53795,7 +55699,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
+          <t>2026-08-04T07:11:12</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -53803,27 +55707,27 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>30292481</t>
+          <t>35671882</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds infected by Pseudomonas aeruginosa (PhagoBurn): a randomised, controlled, double-blind phase 1/2 trial.</t>
+          <t>Novel antimicrobial agents for combating antibiotic-resistant bacteria.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PhagoBurn randomised trial, burn wounds infected by P. aeruginosa</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -53833,39 +55737,35 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>30884879</t>
+          <t>35752612</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
+          <t>Pseudomonas aeruginosa: pathogenesis, virulence factors, antibiotic resistance, interaction with host, technology advances and emerging therapeutics.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>QAMH programme report on processing phage therapy requests; may carry patient outcomes</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -53875,7 +55775,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
+          <t>2026-08-04T07:11:12</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -53883,27 +55783,27 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>31081402</t>
+          <t>35880080</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
+          <t>What Is New in the Anti-Pseudomonas aeruginosa Clinical Development Pipeline Since the 2017 WHO Alert?</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>clinical study of phage therapy in chronic non-healing wound</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -53913,7 +55813,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
+          <t>2026-08-04T07:11:12</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -53921,27 +55821,27 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>31102236</t>
+          <t>36090087</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Successful adjunctive use of bacteriophage therapy for treatment of multidrug-resistant Pseudomonas aeruginosa infection in a cystic fibrosis patient.</t>
+          <t>Treatment of Pseudomonas aeruginosa infectious biofilms: Challenges and strategies.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>case: 26-year-old cystic fibrosis patient, MDR P. aeruginosa pneumonia</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -53951,39 +55851,35 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>31207123</t>
+          <t>36320594</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Early clinical experience of bacteriophage therapy in 3 lung transplant recipients.</t>
+          <t>Therapeutic Bacteriophages for Gram-Negative Bacterial Infections in Animals and Humans.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>case series: three lung transplant recipients with MDR infections</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -53993,39 +55889,35 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>31437402</t>
+          <t>36344073</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy of Ventilator-associated Pneumonia and Empyema Caused by Pseudomonas aeruginosa.</t>
+          <t>Novel Approaches to Multidrug-Resistant Infections in Cystic Fibrosis.</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>no abstract; title reports phage therapy of ventilator-associated pneumonia and empyema</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -54035,39 +55927,35 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>31527029</t>
+          <t>36468950</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic Joint Infection Caused by Multidrug-Resistant Pseudomonas aeruginosa.</t>
+          <t>Bacteriophages: An Alternative to Combat Antibiotic Resistance?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>case: chronic relapsing periprosthetic joint infection and femoral osteomyelitis</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -54077,39 +55965,35 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>31693655</t>
+          <t>36748497</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lytic Bacteriophage Screening Strategies for Multidrug-Resistant Bloodstream Infections in a Burn Intensive Care Unit.</t>
+          <t>Challenges and opportunities in the development of novel antimicrobial therapeutics for cystic fibrosis.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>burn ICU bloodstream infections where screening 'resulted in treatment using bacteriophage'</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -54119,7 +56003,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
+          <t>2026-08-04T07:11:12</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -54127,27 +56011,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>32380707</t>
+          <t>35931928</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
+          <t>Current knowledge in the use of bacteriophages to combat infections caused by Pseudomonas aeruginosa in cystic fibrosis.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>cardiothoracic surgical infections treated with phage</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -54157,39 +56041,35 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>32657966</t>
+          <t>36584930</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
+          <t>Coping with the ESKAPE pathogens: Evolving strategies, challenges and future prospects.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>transplant infection review citing recent published cases; possible case source</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -54199,7 +56079,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
+          <t>2026-08-04T07:11:12</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -54207,27 +56087,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>33005701</t>
+          <t>36898591</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriophage Therapy to Treat Multidrug-Resistant Bacterial Infections at a Single Center in the United States.</t>
+          <t>Phage-based therapy against biofilm producers in gram-negative ESKAPE pathogens.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>first 10 consecutive intravenous phage therapy cases at one centre</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -54237,39 +56117,35 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>33755148</t>
+          <t>37508185</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phage Are All the Rage: Bacteriophage in Clinical Practice.</t>
+          <t>Bacteriophage-Antibiotic Combination Therapy against Pseudomonas aeruginosa.</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>no abstract; clinical-practice piece that may be case-based</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -54279,7 +56155,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
+          <t>2026-08-04T07:11:12</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -54287,27 +56163,27 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>34026768</t>
+          <t>37598024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Case Report: Arthroscopic "Debridement Antibiotics and Implant Retention" With Local Injection of Personalized Phage Therapy to Salvage a Relapsing Pseudomonas Aeruginosa Prosthetic Knee Infection.</t>
+          <t>A systematic review on the use of bacteriophage in treating Staphylococcus aureus and Pseudomonas aeruginosa infections in cystic fibrosis.</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>case: 88-year-old with relapsing Pseudomonas prosthetic knee infection</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -54317,39 +56193,35 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>34177601</t>
+          <t>37644177</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Case Report: Chronic Bacterial Prostatitis Treated With Phage Therapy After Multiple Failed Antibiotic Treatments.</t>
+          <t>[New developments in the fight against bacterial infections : Update on antiobiotic research, development and treatment].</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>case: chronic bacterial prostatitis treated with phage after antibiotic failure</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -54359,7 +56231,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
+          <t>2026-08-04T07:11:12</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -54367,27 +56239,27 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>34369652</t>
+          <t>37770166</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
+          <t>Phages for treatment Pseudomonas aeruginosa infection.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>FULLTEXT</t>
+          <t>EXCLUDE</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>adjunctive phage in a 7-year-old with chronic P. aeruginosa osteoarticular infection</t>
+          <t>narrative or systematic review with no primary patient data of its own</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -54397,59 +56269,5135 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-08-04T07:03:21</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>37843118</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Priorities and Progress in Gram-negative Bacterial Infection Research by the Antibacterial Resistance Leadership Group.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>37843121</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>The Antibacterial Resistance Leadership Group: Scientific Advancements and Future Directions.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>37931230</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Jumbo phages are active against extensively drug-resistant eyedrop-associated Pseudomonas aeruginosa infections.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>in vitro or preclinical activity testing against isolates; no patients treated</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>37997873</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Present and future of resistance in Pseudomonas aeruginosa: implications for treatment.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>38016738</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Bacteriophage treatment as an alternative therapy for multidrug-resistant bacteria.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>38045026</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>A mechanism-based pathway toward administering highly active N-phage cocktails.</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>laboratory study: genome announcement, formulation, cocktail design or platform technology; no patients treated</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>37967634</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bacteriophages: Status quo and emerging trends toward one health approach.</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>38261031</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Phage therapy in lung infections caused by multidrug-resistant Pseudomonas aeruginosa - A literature review.</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>38280761</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Novel Approaches to Multidrug-Resistant Infections in Cystic Fibrosis.</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>38284691</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Strategies to Overcome Antimicrobial Resistance in Nosocomial Infections, A Review and Update.</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>38345396</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Bacteriophages for bronchiectasis: treatment of the future?</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>38391505</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Advances in Development of Novel Therapeutic Strategies against Multi-Drug Resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>38646632</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Antimicrobial resistance of Pseudomonas aeruginosa: navigating clinical impacts, current resistance trends, and innovations in breaking therapies.</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>38786114</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Use of the Naturally Occurring Bacteriophage Grouping Model for the Design of Potent Therapeutic Cocktails.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>laboratory study: genome announcement, formulation, cocktail design or platform technology; no patients treated</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>38787276</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Phage Therapy for Cardiac Implantable Electronic Devices and Vascular Grafts: A Targeted Literature Review.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>38934592</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Optimizing bacteriophage treatment of resistant Pseudomonas.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>38992046</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>High throughput platform technology for rapid target identification in personalized phage therapy.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>laboratory study: genome announcement, formulation, cocktail design or platform technology; no patients treated</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>39017931</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Phage therapy: an alternative treatment modality for MDR bacterial infections.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>39066214</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Pseudomonas aeruginosa Bacteriophages and Their Clinical Applications.</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>39072666</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Pharmacokinetics and pharmacodynamics of bacteriophage therapy: a review with a focus on multidrug-resistant Gram-negative bacterial infections.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>39091071</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>The Guardian of Vision: Intelligent Bacteriophage-Based Eyedrops for Clinical Multidrug-Resistant Ocular Surface Infections.</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>in vitro or preclinical activity testing against isolates; no patients treated</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>39104636</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Understanding and treating diabetic foot ulcers: Insights into the role of cutaneous microbiota and innovative therapies.</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>narrative or systematic review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>39125890</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Phage Therapy: An Alternative Approach to Combating Multidrug-Resistant Bacterial Infections in Cystic Fibrosis.</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>39452768</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Phage-Based Therapy in Combination with Antibiotics: A Promising Alternative against Multidrug-Resistant Gram-Negative Pathogens.</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>39482746</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Current status of bacteriophage therapy for severe bacterial infections.</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>39518670</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Therapeutic Interventions for Pseudomonas Infections in Cystic Fibrosis Patients: A Review of Phase IV Trials.</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>39545100</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Phage Therapy Against Antibiotic-Resistant and Multidrug-Resistant Infections Involving Nonhealing Wounds and Prosthetic Joint Infections Associated With Biofilms: A Mini-Review.</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>40255216</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>What Are the Optimal Irrigating Wound Vacuum Parameters When Using Bacteriophage Therapeutics?</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>methodological, survey or in vitro work; no patient outcomes reported</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>40284749</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Antibiotic-Resistant Pseudomonas aeruginosa: Current Challenges and Emerging Alternative Therapies.</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>40413913</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Phage therapy: A novel approach to combat drug-resistant pathogens.</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>40426494</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Overcoming Pseudomonas aeruginosa in Chronic Suppurative Lung Disease: Prevalence, Treatment Challenges, and the Promise of Bacteriophage Therapy.</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>40478338</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy to combat MDR non-fermenting Gram-negative bacteria causing nosocomial infections: recent progress and challenges.</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>40488994</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Novel therapeutic strategies targeting infections caused by P. aeruginosa biofilm.</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>40596887</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Efficacy of phage therapy in Diabetic Foot Ulcers (DFUs): a systematic review.</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>secondary synthesis (systematic or scoping review); usable for citation-chasing but not a primary study</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>40635382</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Phage-Antibiotic Combinations for Pseudomonas: Successes in the Clinic and In Vitro Tenuously Connected.</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>40781777</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>The potential of bacteriophages in treating multidrug-resistant ESKAPE pathogen infections.</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>40854749</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>[Current status and future prospects of antibacterial treatment for Carbapenem-resistant gram-negative bacterial infections in solid organ transplant recipients].</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>40976373</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Phage therapy: An international survey of attitudes and experiences amongst clinicians.</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>methodological, survey or in vitro work; no patient outcomes reported</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>40979551</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Revolutionizing diabetic foot ulcer treatment: phage therapy as a next-generation antimicrobial approach- a review on breaking the cycle of resistance.</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>41065368</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Current and future options for the treatment of serious infections due to carbapenem-resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>41089845</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Antibiotic-sparing strategies for multidrug-resistant organism (MDRO) infections.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>41139254</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Review: Targeting multidrug-resistant pneumonia: The potential of combined antibiotic therapies and non-antimicrobial approaches.</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>41156622</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Phage to ESKAPE: Personalizing Therapy for MDR Infections-A Comprehensive Clinical Review.</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>41334893</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Beyond Antibiotics: Emerging Therapies for Pseudomonas aeruginosa in Diabetic Foot Infections.</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>41648009</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Multidrug-resistant Pseudomonas aeruginosa infections: current status, challenges, and prospects of phage therapy.</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>41323151</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Phage Therapy for Hospital-Acquired Respiratory Bacterial Infections: A Review.</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>41412007</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>A review of phage therapy for drug-resistant Pseudomonas aeruginosa infections.</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>41597449</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Mechanisms of Pseudomonas aeruginosa Resilience Against Antibiotic Treatment and Outlooks of Emerging Treatment Strategies.</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>41750423</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Phage-Based Approaches to Chronic Pseudomonas aeruginosa Lung Infection in Cystic Fibrosis.</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>41781219</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Cystic fibrosis year in review 2025.</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>41881246</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Phage therapy in people with cystic fibrosis: A systematic review.</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>secondary synthesis (systematic or scoping review); usable for citation-chasing but not a primary study</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>41887374</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Mapping the clinical use of inhaled bacteriophages in respiratory infections caused by multidrug-resistant pathogens: a scoping review.</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>secondary synthesis (systematic or scoping review); usable for citation-chasing but not a primary study</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>41908588</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Management of Diabetic Foot Infections Using Phage Therapy.</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>42029769</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Pseudomonas aeruginosa: associated pathogenesis, epidemiology, resistance mechanisms, host response and emerging treatment strategies.</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>42044976</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Combating Pseudomonas aeruginosa biofilms: Pathogenesis, resistance mechanisms and novel treatment approaches in an era of emerging antimicrobial resistance.</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>42071311</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Phage Therapy as an Alternative Strategy Against Pseudomonas aeruginosa: A Narrative Review of Preclinical and Clinical Evidence.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>42168489</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CApEsid biOfilm: a suggested pipeline for clinical phage microbiology for biofilm infections based on comparative method study.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>methodological, survey or in vitro work; no patient outcomes reported</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>42198401</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Phage Therapy in Combating Multidrug-Resistant Gram-Negative Pathogens: A Scoping Review.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>secondary synthesis (systematic or scoping review); usable for citation-chasing but not a primary study</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>42283824</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy for multidrug-resistant bacterial infections: recent advances, clinical evidence, and translational challenges.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>42291894</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Efficacy and Safety Outcomes of Bacteriophage Therapy for Resistant Bacterial Infections.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>secondary synthesis (systematic or scoping review); usable for citation-chasing but not a primary study</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>42299205</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Pseudomonas aeruginosa in Ventilator-Associated Pneumonia: A Comprehensive Review of Resistance and Clinical Outcomes.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>42353674</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>The ESKAPE Challenge: Understanding Resistance and Exploring Alternative Treatments.</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>EXCLUDE</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>narrative review with no primary patient data of its own</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>28583189</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Use of bacteriophages in the treatment of colistin-only-sensitive Pseudomonas aeruginosa septicaemia in a patient with acute kidney injury-a case report.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>no abstract; title reports phage treatment of septicaemia in a named patient</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>28992111</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Refractory Pseudomonas Bacteremia in a 2-Year-Old Sterilized by Bacteriophage Therapy.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>case: pediatric refractory MDR P. aeruginosa bacteraemia, 2-phage cocktail</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>29588855</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Phage treatment of an aortic graft infected with Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>case: prosthetic vascular graft infection treated with phage</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>30060002</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Innovations for the treatment of a complex bone and joint infection due to XDR Pseudomonas aeruginosa including local application of a selected cocktail of bacteriophages.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>no abstract; title reports XDR P. aeruginosa bone and joint infection with local phage</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>30131795</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Adapted Bacteriophages for Treating Urinary Tract Infections.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>adapted phages for urinary tract infection; abstract does not settle whether patients were treated</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>30292481</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Efficacy and tolerability of a cocktail of bacteriophages to treat burn wounds infected by Pseudomonas aeruginosa (PhagoBurn): a randomised, controlled, double-blind phase 1/2 trial.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>PhagoBurn randomised trial, burn wounds infected by P. aeruginosa</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>30884879</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Lessons Identified.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>QAMH programme report on processing phage therapy requests; may carry patient outcomes</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>31081402</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>clinical study of phage therapy in chronic non-healing wound</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>31102236</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Successful adjunctive use of bacteriophage therapy for treatment of multidrug-resistant Pseudomonas aeruginosa infection in a cystic fibrosis patient.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>case: 26-year-old cystic fibrosis patient, MDR P. aeruginosa pneumonia</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>31207123</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Early clinical experience of bacteriophage therapy in 3 lung transplant recipients.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>case series: three lung transplant recipients with MDR infections</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>31437402</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy of Ventilator-associated Pneumonia and Empyema Caused by Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>no abstract; title reports phage therapy of ventilator-associated pneumonia and empyema</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>31527029</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Bacteriophages as Adjuvant to Antibiotics for the Treatment of Periprosthetic Joint Infection Caused by Multidrug-Resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>case: chronic relapsing periprosthetic joint infection and femoral osteomyelitis</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>31693655</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Lytic Bacteriophage Screening Strategies for Multidrug-Resistant Bloodstream Infections in a Burn Intensive Care Unit.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>burn ICU bloodstream infections where screening 'resulted in treatment using bacteriophage'</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>32380707</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy for Critical Infections Related to Cardiothoracic Surgery.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>cardiothoracic surgical infections treated with phage</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>32657966</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>transplant infection review citing recent published cases; possible case source</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>33005701</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Lessons Learned From the First 10 Consecutive Cases of Intravenous Bacteriophage Therapy to Treat Multidrug-Resistant Bacterial Infections at a Single Center in the United States.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>first 10 consecutive intravenous phage therapy cases at one centre</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>33755148</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Phage Are All the Rage: Bacteriophage in Clinical Practice.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>no abstract; clinical-practice piece that may be case-based</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>34026768</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Case Report: Arthroscopic "Debridement Antibiotics and Implant Retention" With Local Injection of Personalized Phage Therapy to Salvage a Relapsing Pseudomonas Aeruginosa Prosthetic Knee Infection.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>case: 88-year-old with relapsing Pseudomonas prosthetic knee infection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>34177601</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Case Report: Chronic Bacterial Prostatitis Treated With Phage Therapy After Multiple Failed Antibiotic Treatments.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>case: chronic bacterial prostatitis treated with phage after antibiotic failure</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>34369652</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Bacterial lysis, autophagy and innate immune responses during adjunctive phage therapy in a child.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>adjunctive phage in a 7-year-old with chronic P. aeruginosa osteoarticular infection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:03:21</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>34696331</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>Phage Therapy Experience at the Eliava Phage Therapy Center: Three Cases of Bacterial Persistence.</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>FULLTEXT</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>retrospective descriptive study of three patients at the Eliava centre</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F148" t="inlineStr">
         <is>
           <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>2026-08-04T07:03:21</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>35444073</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy for empyema caused by carbapenem-resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>case: post-pneumonectomy empyema with broncho-pleural fistula, carbapenem-resistant</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>35529052</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Combination of phage therapy and cefiderocol to successfully treat Pseudomonas aeruginosa cranial osteomyelitis.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>case: 25-year-old, cranial osteomyelitis after electrocution, phage plus cefiderocol</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>35547216</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Use of Phage Cocktail BFC 1.10 in Combination With Ceftazidime-Avibactam in the Treatment of Multidrug-Resistant Pseudomonas aeruginosa Femur Osteomyelitis-A Case Report.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>case: post-traumatic femoral osteomyelitis, BFC 1.10 with ceftazidime-avibactam</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>35869081</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Personalized bacteriophage therapy to treat pandrug-resistant spinal Pseudomonas aeruginosa infection.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>case: pandrug-resistant spinal bone and joint infection, personalised phage</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>36175406</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Bacteriophage-antibiotic combination therapy against extensively drug-resistant Pseudomonas aeruginosa infection to allow liver transplantation in a toddler.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>case: XDR P. aeruginosa infection treated to allow liver transplantation</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>36578069</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis colonized with Pseudomonas aeruginosa: study protocol for a phase 1b/2, multicenter, randomized, double-blind, placebo-controlled trial.</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>randomised placebo-controlled trial protocol, single intravenous dose, ~72 adults with cystic fibrosis</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>36082999</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Development of Host Immune Response to Bacteriophage in a Lung Transplant Recipient on Adjunctive Phage Therapy for a Multidrug-Resistant Pneumonia.</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>lung transplant recipient on adjunctive phage; phage-specific CD4 T cells and immunoglobulin</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>36636832</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>First-in-human application of double-stranded RNA bacteriophage in the treatment of pulmonary Pseudomonas aeruginosa infection.</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>first-in-human dsRNA phage phiYY in a 40-year-old with interstitial lung disease</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>36861092</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Application of Phage Therapy in a Case of a Chronic Hip-Prosthetic Joint Infection due to Pseudomonas aeruginosa: An Italian Real-Life Experience and In Vitro Analysis.</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>case: 62-year-old, chronic hip prosthetic joint infection, phage with meropenem</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>37160359</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial and nebulised bacteriophage treatment in children with cystic fibrosis and Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>single-arm open-label trial, intrabronchial and nebulised phage in children with cystic fibrosis</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>37243293</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Successful Bacteriophage-Antibiotic Combination Therapy against Multidrug-Resistant Pseudomonas aeruginosa Left Ventricular Assist Device Driveline Infection.</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>case: left ventricular assist device infection, phage-antibiotic combination</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>37275366</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Case report: Analysis of phage therapy failure in a patient with a Pseudomonas aeruginosa prosthetic vascular graft infection.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>case: phage therapy failure in prosthetic vascular graft infection, PT07/14-01/PNM</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>37369702</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Personalized aerosolised bacteriophage treatment of a chronic lung infection due to multidrug-resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>case: 41-year-old with Kartagener syndrome, aerosolised personalised phage</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>37409241</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Refractory Pseudomonas aeruginosa Bronchopulmonary Infection After Lung Transplantation for Common Variable Immunodeficiency Despite Maximal Treatment Including IgM/IgA-Enriched Immunoglobulins and Bacteriophage Therapy.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>case: refractory bronchopulmonary infection after lung transplant for common variable immunodeficiency</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>37515541</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy for Pan-Drug-Resistant Pseudomonas aeruginosa in Two Persons With Cystic Fibrosis.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>two persons with cystic fibrosis, pandrug-resistant P. aeruginosa</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>37562400</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Refractory Pseudomonas aeruginosa infections treated with phage PASA16: A compassionate use case series.</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>compassionate-use case series treated with phage PASA16</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>38066373</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respiratory Tract of an Infant.</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>case: 3-month-old girl, severe bronchitis after tracheostomy, consecutive phage and antibiotics</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>38302552</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Optimized preparation pipeline for emergency phage therapy against Pseudomonas aeruginosa at Yale University.</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Yale emergency phage therapy preparation pipeline; programme report with treated patients</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>38305316</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>[Not Available].</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>title was a placeholder; abstract confirms a case report of chronic relapsing prosthetic aortic graft infection treated with two lytic antipseudomonal phages</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>38470133</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Pseudomonas aeruginosa ventricular assist device infections: findings from ineffective phage therapies in five cases.</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>retrospective series: five ventricular assist device infections, ineffective phage therapy</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>38917792</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Neutralizing antibodies after nebulized phage therapy in cystic fibrosis patients.</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>neutralising antibodies after nebulised phage therapy in cystic fibrosis patients</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>39066242</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Phage Therapy in a Burn Patient Colonized with Extensively Drug-Resistant Pseudomonas aeruginosa Responsible for Relapsing Ventilator-Associated Pneumonia and Bacteriemia.</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>case: burn patient, XDR P. aeruginosa relapsing ventilator-associated pneumonia</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>39074617</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Safety and tolerability of bronchoscopic and nebulised administration of bacteriophage.</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>safety, tolerability and potential efficacy of bronchoscopic and nebulised phage administration</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:11:12</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>39452183</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Phage-Antibiotic Combination Therapy against Recurrent Pseudomonas Septicaemia in a Patient with an Arterial Stent.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>case: recurrent Pseudomonas septicaemia with arterial stent, phage-meropenem</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>39491599</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Access to phage therapy at Hospices Civils de Lyon in 2022: Implementation of the PHAGEinLYON Clinic programme.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>PHAGEinLYON programme; all 2022 phage therapy requests collected prospectively</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>39740667</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Randomized double-blind study on safety and tolerability of TP-102 phage cocktail in patients with infected and non-infected diabetic foot ulcers.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>randomised double-blind trial of TP-102 in patients with diabetic foot ulcers</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>39834667</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Successful Treatment of a Patient With Chronic Bronchiectasis Using an Induced Native Phage Cocktail: A Case Report.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>case: chronic bronchiectasis treated with an induced native phage cocktail</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>39861912</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Phage Therapy as a Rescue Treatment for Recurrent Pseudomonas aeruginosa Bentall Infection.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>case: recurrent P. aeruginosa Bentall endocarditis, phage as rescue</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>39965256</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy for Chronic Mastoiditis.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>case: 47-year-old, intratympanic phage for chronic mastoiditis from MDR P. aeruginosa</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>40301561</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Personalized inhaled bacteriophage therapy for treatment of multidrug-resistant Pseudomonas aeruginosa in cystic fibrosis.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>personalised inhaled phage for MDR P. aeruginosa in cystic fibrosis</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>40368965</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Adjunctive phage therapy improves antibiotic treatment of ventilator-associated-pneumonia with Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>adjunctive phage in ventilator-associated pneumonia</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>40593506</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Phage therapy with nebulized cocktail BX004-A for chronic Pseudomonas aeruginosa infections in cystic fibrosis: a randomized first-in-human trial.</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>BX004-A randomised first-in-human trial in cystic fibrosis</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>40639454</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>A feasibility study for personalized phage therapy against drug-resistant bacteria in Japan.</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>observational feasibility study of personalised phage therapy in Japan</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>40899889</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>[Clinical efficiency of polyvalent piobacteriophage in the complex treatment of nosocomial sinusitis].</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>polyvalent pyobacteriophage in 30 intensive-care patients with nosocomial sinusitis</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>40975185</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and proposed solutions.</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>no abstract; cannot be judged, advanced rather than excluded</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>41022989</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>A case report of bacteriophage therapy for the treatment of lung infection due to carbapenem-resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>case report: phage for carbapenem-resistant P. aeruginosa lung infection</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>41244966</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Resolution of acute rejection in a bilateral double-lung transplanted cystic fibrosis patient following phage intervention.</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>case: acute rejection resolved in a bilateral lung transplant recipient after phage</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>41479406</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Phage therapy of perinephric abscess in kidney transplantation recipients caused by drug-resistant Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>two cases: perinephric abscess in kidney transplant recipients</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>40810649</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy in clinical practice: case studies of Pseudomonas aeruginosa infections.</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>clinical practice case studies of P. aeruginosa infections</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>41510198</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Pharmacodynamic individualization of phage therapy against a KPC-5-producing Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>pharmacodynamic individualisation against a KPC-5-producing isolate; clinical assessment</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>41513696</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Timely bespoke phage-antibiotic combination to treat refractory Pseudomonas aeruginosa mediastinitis and vascular graft infection.</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>case: refractory mediastinitis and vascular graft infection, bespoke phage-antibiotic</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>41565011</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Successful Bacteriophage Treatment of a Recalcitrant Intra-Abdominal Infection Caused by Multidrug-Resistant Pseudomonas aeruginosa in a 2-Year-Old Child.</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>case: recalcitrant intra-abdominal MDR infection in a paediatric patient</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>41589298</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Pan-Resistant Pseudomonas aeruginosa Septic Shock in a Critically Ill Patient: A Case Report.</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>case report: pan-resistant P. aeruginosa septic shock in a critically ill patient</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>41667461</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ecological partitioning enables phage-antibiotic cooperation in a human Pseudomonas infection.</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>longitudinal multiomic case analysis of a man in his seventies on phage-antibiotic therapy</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>41853116</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infection with adjunctive bacteriophage therapy.</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>clearance of hypermutator XDR Pseudomonas osteomyelitis and hardware infection</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>42070625</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Adjuvant multisite bacteriophage cocktail administration as salvage treatment in a patient with a multidrug-resistant Pseudomonas aeruginosa frontal relapsing complex osteitis.</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>case: 37-year-old man, multisite phage cocktail salvage for MDR bone infection</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>42263718</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Calciphylaxis complicated by NDM-1-producing Pseudomonas aeruginosa: first experience with cefepime-zidebactam alongside phage therapy in the USA.</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>case: calciphylaxis with NDM-1 P. aeruginosa, cefepime-zidebactam alongside phage</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>42364990</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Chronic suppression of a multidrug-resistant Pseudomonas aeruginosa in prosthetic joint infection using personalized bacteriophage treatment.</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>FULLTEXT</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>chronic suppression of MDR P. aeruginosa prosthetic joint infection with personalised phage</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>claude-opus-5 (abstract stage, LLM-assisted; pending human verification)</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-08-04T07:12:18</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H66"/>
+  <autoFilter ref="A1:H196"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/quality_reports/cribado.xlsx
+++ b/quality_reports/cribado.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>10.1093/femsle/fnv242</t>
+          <t>10.1186/s13054-017-1709-y</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10.1016/S0749-0690(18)30446-4</t>
+          <t>10.3389/fmicb.2018.01832</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10.3389/fmicb.2014.00051</t>
+          <t>10.1128/AAC.00924-19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10.1371/journal.pone.0051017</t>
+          <t>10.3390/v11030265</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10.1080/21597081.2016.1251379</t>
+          <t>10.3390/antibiotics9050232</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.1128/aac.00954-17</t>
+          <t>10.1097/QCO.0000000000000658</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10.1007/s15010-017-1077-1</t>
+          <t>10.3389/fmed.2021.569159</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>10.1097/qco.0000000000000024</t>
+          <t>10.3389/fphar.2021.692614</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10.1186/s13073-018-0525-6</t>
+          <t>10.3390/v13101901</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>10.1093/nar/gkx343</t>
+          <t>10.1038/s41467-022-33294-w</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10.3389/fphar.2020.578823</t>
+          <t>10.1038/s41467-022-31837-9</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10.1016/S1473-3099(20)30330-3</t>
+          <t>10.1186/s13063-022-07047-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10.3389/fmed.2020.00342</t>
+          <t>10.3389/fmed.2022.851310</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10.1101/2023.01.23.22283996</t>
+          <t>10.1177/23247096231188243</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10.1007/978-1-60327-164-6_7</t>
+          <t>10.3389/fmed.2023.1199657</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>10.1093/jac/dkr198</t>
+          <t>10.1038/s41467-023-39370-z</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10.1111/bph.15526</t>
+          <t>10.2147/IDR.S413900</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10.1016/j.resmic.2018.05.001</t>
+          <t>10.1136/bmjresp-2022-001360</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10.1038/s41467-021-22814-9</t>
+          <t>10.3390/v15051210</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>10.1016/j.chembiol.2022.06.003</t>
+          <t>10.1038/s41598-024-52192-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>10.1016/j.chom.2017.06.018</t>
+          <t>10.3390/v16071080</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>10.3389/fmicb.2019.01674</t>
+          <t>10.3390/antibiotics13100916</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>10.1128/mbio.02441-21</t>
+          <t>10.1128/aac.01728-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>10.1128/cmr.00138-00118</t>
+          <t>10.1016/j.virusres.2024.199442</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>10.1007/978-1-60327-164-6_14</t>
+          <t>10.1007/978-1-0716-3523-0_15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10.1186/2052-0492-1-2</t>
+          <t>10.1038/s41598-025-17510-3</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>10.1016/j.ijantimicag.2023.106856</t>
+          <t>10.1038/s41467-025-59806-y</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>10.1128/aac.02071-21</t>
+          <t>10.3390/v17010123</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>10.1093/gigascience/giac076</t>
+          <t>10.1038/s41467-025-60598-4</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>10.1038/s41591-021-01403-9</t>
+          <t>10.1128/asmcr.00058-24</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>10.1093/jacamr/dlac046</t>
+          <t>10.1128/asmcr.00108-25</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10.1093/bioinformatics/btt656</t>
+          <t>10.1038/s41467-026-69247-w</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10.3390/ph14101019</t>
+          <t>10.1093/jacamr/dlaf257</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>10.1128/jcm.22.6.996-1006.1985</t>
+          <t>10.1038/s41467-025-68136-y</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
